--- a/projects/flatkey/cia/data.xlsx
+++ b/projects/flatkey/cia/data.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -635,70 +635,247 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>81100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2973</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="D2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>theaiconsultinglab</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Did you know that both Anthropic and OpenAI have prompt generator tools that can save you probably 90-95% of time writing prompts for LLM's? 
+*Disclaimer* you will need to create an account on their developer platform and fund it with $5, but there is no ongoing fee to access this platform, and the $5 will go a LONG way for creating prompts.
+Prompt engineering is important, there's no doubt about that, but the model companies are making more progress towards a world where it becomes less important. With every new model that comes out, the reliance on well structured and engineered prompts becomes less important because the models get better at understanding user intents. On top of that, we could start seeing some of these companies implement a type of workflow similar to this prompt generator tool, which translates your requests into well structured prompts automatically. 
+You will still need to be able to diagnose and troubleshoot your prompts if they don't produce the desired result, but using these tools can save you a massive amount of time. For most of my use cases, I will typically use the Anthropic console to write my prompts, and it requires very little editing. 
+Have you tried these tools out yet, if so, what are your impressions of the quality of the prompts they produce? 
+#ai #chatgpt #aiconsulting #llm #deepseek #claude #openai</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@theaiconsultinglab/video/7472894662848662830</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-02-18T22:48:27.000Z</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>62400</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3058</v>
+      </c>
+      <c r="C3" t="n">
+        <v>948</v>
+      </c>
+      <c r="D3" t="n">
+        <v>258</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>nanmadbouly</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>فيه أكتر من provider بيقدموا access مجاني لـ LLMs عن طريق API.
+الـ Repo ده بيتحدث باستمرار وفيه الـ rate limits وكل التفاصيل.
+اللي شغال على AI products ومحتاج يجرب models مختلفة قبل ما يقرر يدفع، ده المكان الصح يبدأ منه.
+#explore #ai #aitools #artificialintelligence</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nanmadbouly/video/7606333545354710290</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-02-13T12:58:59.000Z</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>31200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1167</v>
+      </c>
+      <c r="C4" t="n">
+        <v>358</v>
+      </c>
+      <c r="D4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>marcinteodoru</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>How I Saved $500/Month with ChatLLM ( All-in-One Ai Tool ) 🔥 All-in-One Features (What Makes ChatLLM Unique) ChatLLM combines generative AI, automation, and data analysis into a single platform, eliminating the need for multiple subscriptions. Here’s everything it includes:  💡 Core AI Capabilities ✅ Access to ALL State-of-the-Art LLMs  GPT-4o, Claude Sonnet-3.5, Gemini 1.5, Mistral, Llama 3, and more (always updated). Switch models on the fly for optimal performance. ✅ Real-Time Web Search  Get up-to-date answers (unlike static ChatGPT). ✅ Document Chat  Upload and analyze PDFs, Word, Excel, PPTs (summarize, extract data, Q&amp;A). ✅ Code Generation &amp; Execution. #LLM #LargeLanguageModels #ChatGPT #GPT4 #ClaudeAI #Claude3 #GeminiAI #Gemini1.5 #PerplexityAI #MistralAI #Mixtral #LLaMA #LLaMA2 #LLaMA3 #Groq #CommandR #ChatLLM #OpenAI #Anthropic #GoogleDeepMind #MetaAI #CohereAI #AIModels #AIComparison #LLMShowdown #AIStack #AIBattle #MarcinAI #TechTok #AITools #airevolution</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@marcinteodoru/video/7486218137122163999</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-03-26T20:30:33.000Z</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>25000</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B5" t="n">
         <v>939</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C5" t="n">
         <v>264</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D5" t="n">
         <v>34</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E5" t="n">
         <v>0.01056</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>stevemorinnyc</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>AI Open Source 
 Google LLM Model
 Built for Business #openai #gemini #ai #aitools #chatgpt</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@stevemorinnyc/video/7538614750335225118</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2025-08-15T01:15:39.000Z</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>12600</v>
+      </c>
+      <c r="B6" t="n">
+        <v>445</v>
+      </c>
+      <c r="C6" t="n">
+        <v>129</v>
+      </c>
+      <c r="D6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nicksadler.io</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Learn OpenAI's secret reverse prompting technique that transforms mediocre AI outputs into elite results by showing examples instead of guessing prompts.
+#ai #chatgpt #promptengineering #aitools #contentcreation</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nicksadler.io/video/7589058350235634966</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-12-28T23:42:30.000Z</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>11800</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B7" t="n">
         <v>487</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C7" t="n">
         <v>109</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D7" t="n">
         <v>7</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E7" t="n">
         <v>0.00924</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>dubibubiii</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>OpenRouter just quietly dropped a model called Pony Alpha.
 And nobody knows who made it.
@@ -716,87 +893,87 @@
 Follow if you're building with AI.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@dubibubiii/video/7604737152378850616</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2026-02-09T07:43:02.000Z</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>338</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B8" t="n">
         <v>18</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E8" t="n">
         <v>0.008880000000000001</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>alanonai</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>OpenAI LLMs are now available in AWS Bedrock and SagemakerAI. Does it even matter?
 #ai #techtok #news #llm</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@alanonai/video/7535443863062793502</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2025-08-06T12:10:58.000Z</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>4897</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B9" t="n">
         <v>269</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C9" t="n">
         <v>43</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>0.00878</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>campixl</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Banyak yang tahu ChatGPT, tapi tahu nggak kalau ada versi open-source-nya yang bisa kamu jalankan sendiri?
 Di 2025 ini, model-model seperti Qwen 3, LLaMA 3.3, Mistral, sampai Phi 4 jadi pilihan top buat yang mau bikin AI agent sendiri, tanpa bayar API!
@@ -805,128 +982,178 @@
 #openai #opensourceai #llm #aiteknologi #aiindonesia #belajarai #techcontent #machinelearning #qwen3 #mistral #llama3 #gemma3 #ai #deepseek #claude #qwen #microsoft #phi #gemma #google #artificelintelligence #opensource #openweight #llama</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@campixl/video/7503530696510606600</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2025-05-12T12:11:25.000Z</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>21000</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" t="n">
         <v>830</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" t="n">
         <v>183</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D10" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E10" t="n">
         <v>0.008710000000000001</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>github.awesome</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>OpenChronicle is A self-hosted interaction engine that makes your LLM conversations durable. Persistent long-term memory, deterministic tasking, and fully auditable decision trails injected directly into your workflow. Totally provider-agnostic. Plug in any model you want. Seamlessly supports your local CLI, Discord bots, and MCP servers out of the box. #github #opensource</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@github.awesome/video/7633612206290046222</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2026-04-28T01:14:31.000Z</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>23200</v>
       </c>
-      <c r="B7" t="n">
-        <v>1878</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B11" t="n">
+        <v>1877</v>
+      </c>
+      <c r="C11" t="n">
         <v>159</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D11" t="n">
         <v>46</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E11" t="n">
         <v>0.00685</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>pandurijal</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>LiteLLM buat unlock ratusan model AI di satu tempat | Link: litellm.ai</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@pandurijal/video/7621590335910825217</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2026-03-26T15:43:16.000Z</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>157900</v>
+      </c>
+      <c r="B12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>925</v>
+      </c>
+      <c r="D12" t="n">
+        <v>98</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.00586</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>midudev</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Esta es la mejor alternativa a Claude Code y similares.
+Un agente de IA para programadores.
+Se llama OpenCode y es 100% de código abierto
+✓ Sin coste ni suscripciones
+✓ Usa cualquier modelo, también gratuitos en local
+✓ Compatible con OpenAI, Anthropic, Google...
+Está ganando mucha popularidad ya que las otras opciones son bastante caras.
+¿Qué te parece?
+#software #programacion #programadores #informatica #programador</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@midudev/video/7591896705524616470</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-05T15:16:44.000Z</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>172</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B13" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E13" t="n">
         <v>0.00581</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>capitalledger</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>OpenAI has introduced Open Responses, an open-source specification designed to enable multi-provider, interoperable LLM interfaces.
 Key Features:Simplifies integration of different LLMs without requiring backend rewrites.
@@ -934,44 +1161,44 @@
 #openai #api #support #news #thecapitalledger</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@capitalledger/video/7597164833091390750</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2026-01-19T20:00:02.000Z</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>22600</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B14" t="n">
         <v>794</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C14" t="n">
         <v>124</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E14" t="n">
         <v>0.00549</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>trendingtechtutor</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Open Ai have recently released their prompt engineering guide for their LLM ChatGPT. 
 ——————————————————-
@@ -980,171 +1207,171 @@
 #openai #chatgpt #chatgpt4 #samaltman #promptengineering #artificialintelligence #Ai</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@trendingtechtutor/video/7312888048205745440</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2023-12-15T18:20:35.000Z</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>5482</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B15" t="n">
         <v>196</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C15" t="n">
         <v>29</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D15" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E15" t="n">
         <v>0.00529</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>stardeckth</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>stardeck ต่อระบบ Payment gateway ได้ไหม?!😉✨ 
 #ai #developer #paymentgateway #tech #website</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@stardeckth/video/7599946401480527124</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2026-01-27T07:53:43.000Z</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>926600</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B16" t="n">
         <v>88700</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C16" t="n">
         <v>4689</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D16" t="n">
         <v>705</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E16" t="n">
         <v>0.00506</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>carterpcs</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>OpenAI is working with the department of war!! #carterpcs #tech #openai #pentagon #anthropic</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@carterpcs/video/7612544326777769247</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2026-03-02T06:40:39.000Z</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>44800</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B17" t="n">
         <v>1995</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C17" t="n">
         <v>225</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D17" t="n">
         <v>41</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E17" t="n">
         <v>0.00502</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>hes_a_nerd</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>new LLM capabilities discovered with these prompt tricks #chatgpt #openai #claude #gemini #ai #tech #artificialintelligence #tiktoklearningcampaign</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@hes_a_nerd/video/7497017061382655262</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>2025-04-24T22:55:22.000Z</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>5197</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B18" t="n">
         <v>103</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C18" t="n">
         <v>26</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E18" t="n">
         <v>0.005</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>klingai_official</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Kling AI Skill Now Live!
 No complex configs, no model adaptation! 
@@ -1159,87 +1386,87 @@
 #KlingAI #KlingAISkill</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@klingai_official/video/7628954577211116821</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2026-04-15T12:00:12.000Z</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>36700</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B19" t="n">
         <v>1912</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C19" t="n">
         <v>183</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D19" t="n">
         <v>19</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E19" t="n">
         <v>0.00499</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>leocrunfli</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Esse é o chat LLM
  #inteligenciaartificial #ia #chatllm #ai #techtok</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@leocrunfli/video/7571979706023562504</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>2025-11-12T23:08:36.000Z</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>1074</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B20" t="n">
         <v>55</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C20" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D20" t="n">
         <v>8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E20" t="n">
         <v>0.00466</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>unwind_ai</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Awesome LLM Apps repo on GitHub
 ⭐️ now!
@@ -1248,44 +1475,88 @@
 #ai #aiagent #opensource #mcp #rag</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@unwind_ai/video/7575973417170586910</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>2025-11-23T17:26:23.000Z</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>69400</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2864</v>
+      </c>
+      <c r="C21" t="n">
+        <v>319</v>
+      </c>
+      <c r="D21" t="n">
+        <v>71</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>davidbombal</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DeepSeek &amp; Dolphin: Private &amp; Uncensored local LLMs
+Full Video on my YouTube channel here: https://youtu.be/A2CqSfd5I4I
+#deepseek #chatgpt #openai #ai #ml #privacy #llm #offline</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@davidbombal/video/7469061035870260513</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2025-02-08T14:51:41.000Z</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>16000</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B22" t="n">
         <v>321</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C22" t="n">
         <v>69</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D22" t="n">
         <v>13</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E22" t="n">
         <v>0.00431</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>swiftsyncai</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>This site allows you to access every AI model with just one API Key! 🔐
 It’s called OpenRouter.
@@ -1293,44 +1564,87 @@
 #ai #aiautomation #automation #n8n #n8nautomation #aiagent #openrouter</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@swiftsyncai/video/7534399033381621014</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>2025-08-03T16:36:21.000Z</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B23" t="n">
+        <v>47</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>the.synthetic.mind</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>A quick guide on how to think about LLM optimization. Original source is a talk from OpenAI on “A survey of techniques for maximizing LLM performance”. Look it up on YouTube for more in depth explanations.
+#AI #llm #engineering</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@the.synthetic.mind/video/7532581903249968389</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2025-07-29T19:04:58.000Z</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>282</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B24" t="n">
         <v>8</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C24" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E24" t="n">
         <v>0.00355</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>haseen.dev</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>OpenAI &amp; LLM Providers A Quick Overview
 Artificial Intelligence is evolving fast, and Large Language Model (LLM) providers are leading the revolution. Here’s a simple breakdown:
@@ -1351,129 +1665,215 @@
 #AI #OpenAI #ChatGPT #LLM #Technology</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@haseen.dev/video/7634765993079737618</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>2026-05-01T03:51:28.000Z</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2392</v>
+      </c>
+      <c r="B25" t="n">
+        <v>70</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>nickjunes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Open AI makes the Yamanake factors 50 times more effective using an LLM.  this is an interesting use of the LLM technology and also possibly a very useful tool in Life Extension. I hope to see AI technology used more in this way.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nickjunes/video/7544493048454073631</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2025-08-30T21:26:34.000Z</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>49700</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B26" t="n">
         <v>1657</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C26" t="n">
         <v>147</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D26" t="n">
         <v>150</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E26" t="n">
         <v>0.00296</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>jurnee061</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>It’s Virgo Season!! Here Is My Thoughts On The Compatibility Of Aries &amp; Virgo. I Am Biased Cause I Love My Man 
 #aries #virgo #relationships #zodiac #zodiacsigns c</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@jurnee061/video/7545151026182049055</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>2025-09-01T15:59:48.000Z</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>1804</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B27" t="n">
         <v>100</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C27" t="n">
         <v>5</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E27" t="n">
         <v>0.00277</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>huylamai.code4life.ai</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>#aiengineer #genai #code4life #taovietduc #huylamai</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@huylamai.code4life.ai/video/7636709317160258823</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2026-05-06T09:32:35.000Z</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6616</v>
+      </c>
+      <c r="B28" t="n">
+        <v>361</v>
+      </c>
+      <c r="C28" t="n">
+        <v>18</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.00272</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>calebwritescode</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>OpenAI rushed into releasing their GPT-5.2 model and it has many implication on OpenAI and its conneciton to Oracle and OCI and all the capital structure that's tied to it.
+Let's look at how private credit, AI bubble, and economy fueling the AI investments will shake out. As the AI race continues with OpenAI, Meta, xAI, Anthropic and Google, and TPU and Nvidia and AMD chips are also competing from data center build outs, we will look at how debt based vs capital and capex and cashflow based funding plays out as we go.
+#llm #largelanguagemodels #ai #LLMs #machinelearning #tech #research #explained #artificialintelligence #business #softwareengineer #economy #agi #openai #aibubble #datacenter #oracle #gpt</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@calebwritescode/video/7583628608619547918</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2025-12-14T08:33:38.000Z</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>1104</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B29" t="n">
         <v>26</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C29" t="n">
         <v>3</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D29" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E29" t="n">
         <v>0.00272</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>enodiaudu</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Do you use GitHub Copilot? You will want to try this.
 OpenAI just released Codex - a coding agent that runs directly on your terminal.
@@ -1483,341 +1883,665 @@
 #ai #softwaredeveloper #openai #llm #codex #developer #hacks #terminal</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@enodiaudu/video/7494639239729106198</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2025-04-18T13:08:03.000Z</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>11400</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B30" t="n">
         <v>386</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D30" t="n">
         <v>6</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E30" t="n">
         <v>0.00254</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>startupcode.net</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>OpenRouter: Test 300+ LLMs With One Line of Code
 OpenRouter lets us switch between 300+ LLMs with one line of code! Forget direct integrations with OpenAI or Claude. we can test Gemini, switch to Claude, or use OpenAI effortlessly. See price points and response quality instantly. #OpenRouter #LLMs #AIModels #GeminiAPI #Claude #OpenAI #DevelopmentTools #AICode #MachineLearning #API</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@startupcode.net/video/7509222068932660522</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>2025-05-27T20:17:33.000Z</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>13400</v>
+      </c>
+      <c r="B31" t="n">
+        <v>153</v>
+      </c>
+      <c r="C31" t="n">
+        <v>34</v>
+      </c>
+      <c r="D31" t="n">
+        <v>13</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.00254</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>worldcomputerca</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Portátil Elite 2 en 1 de 14,1", FHD, Intel Core
+17-1165G7, gráficos Intel® Iris Xe, SSD de 256
+GB, 8 GB de RAM, audio espacial THX, cámara de 2 MP, HDMI, lápiz óptico incluido, Windows
+11 Home, azul
+#laptop
+#gateway
+#worldcomputerca
+#laptopmurah</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@worldcomputerca/video/7310314290362240261</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2023-12-08T19:53:06.000Z</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>819</v>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>alphagrowthclub</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>OpenAI’s most secret device just leaked 👀
+Designed by Jony Ive—the mind behind the iPhone.
+Sam Altman paid $6.5B to bring that design power in-house.
+History says this is hard:
+• Meta tried → failed
+• Amazon tried → lost millions
+Because Apple didn’t just build a device—they built an ecosystem over 20 years.
+This won’t kill the iPhone today.
+But this is where the next battle starts.
+Follow 👉 @alphagrowthclub
+No hype. Just clarity, signals &amp; time saved.
+#ai #openai #apple #tech  #innovation</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@alphagrowthclub/video/7635651294606183702</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-05-03T13:06:52.000Z</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>48600</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2853</v>
+      </c>
+      <c r="C33" t="n">
+        <v>76</v>
+      </c>
+      <c r="D33" t="n">
+        <v>24</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.00156</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>sajjaadkhader</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ML vs AI Engineer: Which career to pick ⁉️ #ai #ml #tech #fyp</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sajjaadkhader/video/7603459791868022029</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-02-05T19:07:34.000Z</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>12000</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B34" t="n">
         <v>506</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C34" t="n">
         <v>17</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D34" t="n">
         <v>22</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E34" t="n">
         <v>0.00142</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>prithvinexa</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>#openai #fyp</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@prithvinexa/video/7503945220480830763</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2025-05-13T15:00:39.000Z</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>1462</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B35" t="n">
         <v>30</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C35" t="n">
         <v>2</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E35" t="n">
         <v>0.00137</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>adam.digital</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>OpenAI GPT5.5 Workspace Agent is wild  🔥💯 #chatgpt #openai #aiagent</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@adam.digital/video/7635470179379514645</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>2026-05-03T01:24:06.000Z</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>740</v>
+      </c>
+      <c r="B36" t="n">
+        <v>13</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.00135</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>chaonguoidep65</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>GPT-image-2正式上线#ai生图 #gpt #openai</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@chaonguoidep65/video/7636999202815495442</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-05-07T04:17:35.000Z</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>497200</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B37" t="n">
         <v>44000</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C37" t="n">
         <v>424</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D37" t="n">
         <v>3397</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E37" t="n">
         <v>0.00085</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>yaammari</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Next time I go to the beach I will draw your requests | It’s really not that hard🫩 #art #ai #fyp #viral #xyzabc</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@yaammari/video/7635298998898674966</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>2026-05-02T14:19:47.000Z</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>52800</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B38" t="n">
         <v>1055</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C38" t="n">
         <v>41</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D38" t="n">
         <v>72</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E38" t="n">
         <v>0.00078</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>bataihub</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>There’s an AI chat site where conversations aren’t overly restricted 🤖🔥 You can ask bold questions, explore creative ideas, role-play scenarios, and talk freely without constant refusals 🚫❌. It’s designed for people who want raw, unfiltered conversations — whether that’s deep thoughts, wild ideas, or just curiosity about what AI can really do 🧠💬. No hand-holding. No unnecessary limits. Just you and the chat. Creepy? 😬 Interesting? 👀 Surprisingly addictive? Absolutely 😮🔥 #ai #aitools #chatbot #uncensoredai #techfinds internetculture futureofai</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@bataihub/video/7595052307914525974</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>2026-01-14T03:22:14.000Z</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>4369</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B39" t="n">
         <v>138</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C39" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D39" t="n">
         <v>6</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E39" t="n">
         <v>0.00069</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>techfren</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>aisuite - interface multiple LLMs in one call with the python SDK
 github andrewyng/aisuite
 #litellm #python #openai #api</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@techfren/video/7451931440356314374</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2024-12-24T11:00:03.000Z</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B40" t="n">
+        <v>43</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.00049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>campixl</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Kamu mau bikin AI agent tapi bingung pilih API yang mana?
+Ini 5 LLM API terbaik di tahun 2025 versi risetku:
+	•	OpenAI (GPT-4o): kuat dan multimodal
+	•	Claude (Anthropic): aman dan pintar reasoning
+	•	Gemini (Google): cocok buat multimodal dan integrasi
+	•	Perplexity: real-time, cocok buat AI search
+	•	DeepSeek: jago coding, logic, dan bisa jalanin local
+Ada yang udah kamu coba? Atau masih bingung mau mulai dari mana?
+#openai #llm #chatgpt #gpt4 #chatgpthack #chatgptprompts #ai #aiteknologi #machinelearning #aiindonesia #indonesia #claude #deepseek #preplexity #gemini #api #ai #fypage #fyp #techcontent</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@campixl/video/7505015577639914760</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2025-05-16T12:13:31.000Z</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B41" t="n">
+        <v>30</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>aimakeslifeeasier</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Must have LLM Gateway for AI apps. #aitools #bifrost #ai</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@aimakeslifeeasier/video/7536566808485072158</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2025-08-09T12:48:55.000Z</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>86800</v>
+      </c>
+      <c r="B42" t="n">
+        <v>125</v>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>tiiny.ai.official</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Everyone says "run LLMs locally"…
+But what does the hardware cost?
+Watch closely. Take a guess at the cost of Tiiny and comment below. Tiiny might surprise you.
+🎉 Happy New Year! Let's rethink personal AI in 2026.
+##AI #chatgpt #openai #LLM</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tiiny.ai.official/video/7590965270550695186</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-01-03T03:30:00.000Z</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
         <v>272</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B43" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C43" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D43" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>tayorealmusic</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>**Bifrost surges as 2026's top open-source LLM gateway, unifying 15+ providers with OpenAI-compatible APIs for caching, governance, and seamless model swapping—perfect for devs dodging vendor lock-in and slashing costs on free AI access!** Read the full article: https://medium.com/@tayorealmusic/unlocking-free-llm-apis-two-effortless-methods-for-developers-c819564fe0f8?source=rss-11f4f9862b63------2 #AI #LLM #OpenSource #DevTools #FreeAPI https://medium.com/@tayorealmusic/unlocking-free-llm-apis-two-effortless-methods-for-developers-c819564fe0f8?source=rss-11f4f9862b63------2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@tayorealmusic/video/7600644379593706784</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>2026-01-29T05:03:48.000Z</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>253</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B44" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C44" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>devntell_podcast</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>👀 Did you know there’s now an open-source alternative to OpenRouter?
 LLM Gateway is here to give devs more control over their AI stack 🚀
@@ -1825,44 +2549,44 @@
 #opensourceai #openai #LLM #aitools #aicommunity</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@devntell_podcast/video/7540873837500501265</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>2025-08-21T03:22:48.000Z</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
         <v>173</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B45" t="n">
         <v>5</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C45" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>trophy.boil5</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>EUROPE! We know it’s early days, but it pays to be prepared and the Rut is nearing. 🦌 📢 
 Our Electric Skull Simmering Unit is the ultimate solution for hunters, taxidermists, and outfitters, who value precision and efficiency when preparing skull mounts.
@@ -1880,101 +2604,185 @@
 #huntingnz #huntingaustralia #huntingeurope #huntinguk #euromount</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@trophy.boil5/video/7638412640892538120</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>2026-05-10T23:42:22.000Z</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>306</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B46" t="n">
         <v>3</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C46" t="n">
         <v>0</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D46" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>trishawomochil</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>My family has a tradition: everyone, regardless of gender, must hide their identity and never reveal their family background #stories #novel #NovelMas</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@trishawomochil/video/7638223857027009806</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>2026-05-10T11:29:15.000Z</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>openai compatible llm gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ayainek</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ayainek/video/7635123808482970901</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-05-02T02:59:59.000Z</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>172</v>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>advicetaphanhin019</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>จะไปไหนไกลทำไม ที่นี่ก็มี Advice นะ#CapCutสั่งซื้อสินค้า Inbox #Adviceตะพานหิน😍
+☎️ โทร : 056-611646 , 085-2000070
+🌐 เว็บไซต์ : www.advice.co.th/branch-u019
+✨"แอดไวซ์ ศูนย์รวมไอที สมาร์ทโฟน" จำหน่ายและซ่อม ครบ จบ ในที่เดียว 
+  #Advice #ฟีด #แอดไวซ์ตะพานหิน #สินค้าไอที</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@advicetaphanhin019/video/7636666038968519954</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-05-06T06:44:35.000Z</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>143</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B49" t="n">
         <v>0</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C49" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D49" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>gladysalice19761</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>HAL REACTS TO SEASON OVERCLOCKED! (The Meta Is Changing Forever) #game #streamer #tiktok #viral</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@gladysalice19761/video/7638161471083400479</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>2026-05-10T07:28:11.000Z</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>openai compatible llm gateway</t>
         </is>
@@ -1991,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1999,7 +2807,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
@@ -2135,7 +2943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5132</v>
+        <v>5137</v>
       </c>
       <c r="B4" t="n">
         <v>699</v>
@@ -2172,6 +2980,85 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4917</v>
+      </c>
+      <c r="B5" t="n">
+        <v>131</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ontario</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In the Toronto Star today. LOL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Images:
+	https://preview.redd.it/erega1sv71pg1.jpeg?auto=webp&amp;amp;s=65964e0a1087f45f101fe76aef28128b713953ef</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Top-Manner7261</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/ontario/comments/1rtmspd/in_the_toronto_star_today_lol/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-14T15:48:30.000Z</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4180</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1232</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>StarWars</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>If you had to choose a personal spacecraft from starwars what would it be?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Imagine this: You are a normal citizen of maybe coruscant and are a Bit richer to have your own spaceship and Travel the Galaxy and do everything you please. I would choose the Razor Crest. It’s big, has a bedroom and seems super reliable.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gaspipecat</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/StarWars/comments/1o33hv3/if_you_had_to_choose_a_personal_spacecraft_from/</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-10-10T15:08:01.000Z</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2184,19 +3071,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2248,6 +3135,580 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>query</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2620</v>
+      </c>
+      <c r="B2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The Economic Architect</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LiteLLM Proxy: The 'Universal Adapter' for AI Models</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LiteLLM: The 'Universal Adapter' for AI Models 💡
+Stop struggling with vendor lock-in! The LiteLLM Python SDK and Proxy Server (AI Gateway) let you call 100+ LLMs using a unified, OpenAI-compatible format.
+LiteLLM acts as a standardized proxy, enabling a decoupled architecture so your application logic doesn't need to know which model provider it is using.
+You can seamlessly integrate models from:
+• AWS Bedrock (supporting Anthropic, Meta, Deepseek, Mistral, Amazon, etc.).
+• Azure OpenAI (supporting models like GPT-4o, GPT-5, and O-series).
+• Ollama for local LLMs.
+The LiteLLM Proxy provides essential LLM Gateway features, including:
+• Load Balancing and routing requests across multiple deployments.
+• Cost tracking and setting budgets per project/key.
+• Integration of Guardrails (e.g., using Aporia for PII detection on input or profanity detection on output).
+Decouple your application and optimize your performance today! 🚀
+#LiteLLM #AIGateway #LLMOps #AIInfrastructure #AWSBedrock</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>389</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lktOVpPpRDg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-11-24T06:25:39Z</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>689</v>
+      </c>
+      <c r="B3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Datapizza</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Client Factory &amp; OpenAI-Compatible Endpoints Explained | Datapizza AI Guide (3/8)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>In today's video, Raul, AI R&amp;D Engineer, takes a deep dive into two powerful concepts:
+✅ The ClientFactory class -  a cleaner, configuration-driven way to choose the right provider for each task.
+✅ Working with OpenAI-compatible endpoints - unlock local models with Ollama or vLLM, and seamlessly connect to remote providers like Cerebras, Groq, and DeepSeek.
+🔗 Resources Mentioned:
+GitHub Repository: https://bit.ly/496TOQO
+Official Documentation: https://bit.ly/3J1rLI6
+Join the Community on Discord: https://bit.ly/4918p0d
+👇 Don’t Miss the Next Videos!</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>432</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PHwQQEj8ugA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-11-21T13:30:35Z</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Himanshu</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hybrid LLM Gateway Explaination By Himanshu Haldar</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The Hybrid LLM Gateway is a production-grade infrastructure project designed to act as an intelligent, cost-aware intermediary between user applications and Large Language Models (LLMs). Instead of connecting an application directly to an expensive cloud provider, this gateway sits in the middle to manage where and how AI requests are processed.
+The Core Problems Addressed
+The project was created because most current AI applications suffer from three main issues:
+• High and Unpredictable Costs: Constantly calling premium cloud LLMs for every simple query leads to massive bills.
+• Vendor Lock-in: Applications are often hard-coded to a single provider, making it difficult to switch services.
+• Lack of Control: Developers typically have no control over routing or inference strategies, meaning they cannot choose cheaper options for simple tasks and premium options for complex ones automatically.
+The Need for the Project
+There is a growing need for "AI infrastructure" that prioritizes efficiency and performance rather than just making API calls. This project fulfills that need by providing a self-hosted, OpenAI-compatible inference layer that can be reused across multiple backend or MERN projects. 
+The gateway's primary feature is its Smart Routing system, which decides where to send a request based on specific criteria. A request is escalated from the local Ollama instance to the cloud-based DigitalOcean Agent under the following conditions:
+• Token Count: If the request length exceeds a predefined limit (LOCAL_MAX_TOKENS).
+• Intent Detection: If the system detects that the user's prompt requires "heavy" processing.
+• Explicit Override: If the user specifically requests a high-performance model by setting the modelPreference to "large".
+Technical Infrastructure
+The gateway is built with a modern, high-performance tech stack including Node.js 22, Fastify, and Redis.
+• Security: It features API Key Authentication, where keys are stored and validated via Redis to support rate limiting and daily usage tracking.
+• RAG-Ready: It is compatible with DigitalOcean Agents that have attached Knowledge Bases, making it suitable for Retrieval-Augmented Generation.
+• Deployment: The entire system is Dockerized, allowing for a one-command startup and easy deployment on DigitalOcean Droplets or any Docker-compatible virtual machine.
+Analogy for Understanding
+Think of the Hybrid LLM Gateway like a smart home energy manager. For basic needs like lighting a room, it uses the "local" solar power you’ve already paid for (Ollama). However, if you try to run a heavy appliance like a central air conditioner (a complex AI query), the manager automatically switches to the "cloud" city power grid (DigitalOcean) to ensure you have enough capacity, switching back once the heavy task is over to keep your costs as low as possible.
+The Hybrid LLM Gateway is designed to transform how applications interact with AI by moving away from simple API calls toward a managed, production-grade infrastructure layer. It addresses several critical challenges faced by developers when building modern AI applications.
+1. High and Unpredictable Costs
+Many AI applications suffer from escalating expenses because they "blindly" call expensive cloud LLMs for every interaction. The gateway solves this by prioritizing free local inference through Ollama. By serving simpler requests locally, it significantly reduces the financial burden of running an AI-driven service.
+2. Lack of Routing and Inference Control
+Standard AI integrations often provide no granular control over how or where a model is processed. This project introduces Smart Routing, which makes real-time decisions based on the complexity of the task. It ensures that high-quality cloud inference (via DigitalOcean Gradient™ AI Agents) is only utilized when:
+• The token count exceeds specific limits.
+• The system detects "heavy" intent (complex reasoning or tasks).
+• The user explicitly requests a "large" model preference.
+3. Vendor Lock-in
+A major risk for modern apps is becoming too dependent on a single AI provider's proprietary API. This gateway acts as an OpenAI-compatible inference layer.
+4. Infrastructure and Security Gaps
+Beyond simple connectivity, AI applications need robust management tools to be production-ready. The gateway provides:
+• Performance Optimization: It balances low-latency local inference with high-performance cloud processing.
+• Security and Monitoring: It includes API Key Authentication managed via Redis, which supports essential production features like rate limiting and tracking daily usage limits.
+• Deployment Flexibility: The entire system is Dockerized, allowing it to be easily deployed on DigitalOcean Droplets or any Docker-compatible virtual machine.</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>379</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IcBmp-xVKK0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-01-13T18:21:36Z</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TheDigitalSamajh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Build an Enterprise Grade Local LLM Gateway Solving Cost and Privacy Challenges in AI in 12 Minutes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tired of unpredictable API bills and data privacy concerns? In this deep dive, we move beyond simple chatbots to architect a Local-First Multi-Agent System. I’ll show you how to leverage Ollama as a high-performance gateway and use a custom Orchestration Layer to route queries across specialized agent types—all running 100% offline on a standard 16GB laptop.
+🏗️ What We’re Architecting:
+The Gateway Pattern: Implementing an OpenAI-compatible local server using Ollama.
+Multi-Agent Orchestration: Building a "Manager" agent to classify and route queries with zero creative drift (Temperature 0.0).
+Specialized Agent Strategy: * Deterministic Agents: Pure Python logic for 100% accuracy (Pricing/Data).
+RAG Agents: Grounded retrieval-augmented generation for policy/docs.
+Probabilistic Agents: Generative power for creative recommendations.
+Quantization Deep Dive: Why Q4_K_M is the "Goldilocks" zone for local performance.
+📂 Resources &amp; Code
+GitHub Repository: https://github.com/sharvangkumar/agenticai-privateserver/tree/main/multiagent-privatellma-server 
+👨‍💻 About Me
+I’m Sharvan Kumar, a Full-Stack Solution Architect with over 17 years of experience in technical leadership and system design. My current focus is bridging the gap between Enterprise Architecture and Generative/Agentic AI to build scalable, private-first solutions.
+LinkedIn: https://www.linkedin.com/in/sharvankumar/
+Website: sharvangkumar.github.io
+🛠️ Core Tech Stack
+Ollama: https://ollama.com/ (The local model engine)
+LiteLLM: https://www.litellm.ai/ (Proxy for model abstraction)
+OpenAI Python SDK: (Used to interface with our local gateway)
+Phi-4 &amp; Qwen 2.5 Coder: The backbone models for this architecture.
+#genai  #localllm  #ollama  #multiagentsystems  #enterprisearchitecture  #python  #agenticai  #privacyfirst</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>730</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dOuSVP6_Es4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-03-31T09:45:52Z</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sekademi Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GitHub Trending Repositories: aws-samples/bedrock-access-gateway 🇬🇧</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Your OpenAI code works on Amazon Bedrock instantly
+OpenAI Compatible API Gateway for Amazon Bedrock
+- Converts OpenAI API requests into Amazon Bedrock calls to enable seamless model switching without code changes
+- Provides a bridge for tools like AutoGen to use Bedrock models via standard OpenAI SDKs and RESTful endpoints
+- Implements response streaming through AWS Lambda and API Gateway for real-time interaction and lower latency
+- Seamless OpenAI SDK compatibility for Bedrock models
+- Real-time response streaming with Server-Sent Events
+- Support for multimodal inputs and advanced reasoning models
+#aws #bedrock #openai #ai #cloudcomputing #python #api #machinelearning #github #softwaredevelopment</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gql0tfr8Cn0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-21T04:03:09Z</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Anuchit Chalothorn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dart แบบ Dart Dart EP262: Build Enterprise AI Integrating Agents with Internal APIs via AgentGateway</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>เนื้อหา
+-------
+- เข้าใจเรื่อง Proxy
+- การใช้งาน LLM Gateway เรียกใช้ model หลายๆ ตัว
+- การใช้งานร่วมกับ OpenAI Compatible API, MCP, OpenAPI
+- Logging, Observability
+อย่าลืมอุดหนุนหนังสือ 
+---------------------------------
+ * สูตรลัด Flutter : เขียน Flutter ง่ายๆ จากโค้ดตัวอย่าง
+ * สูตรลัด GetX : ใช้งาน GetX แบบเข้าใจและประยุกต์ใช้ได้จริง
+ * สูตรลัด FlutterFire : เขียน App เชื่อมต่อกับ Firebase ง่ายๆ จากโค้ดตัวอย่าง
+ * สูตรลัด Hasura : สร้าง GraphQL backend โดยไม่ต้องเขียนโค้ด
+ * คู่มือประกอบการเรียน Flutter Crash Course 
+ * Material Design 3 :  ใช้งาน Material Design Widget ใน Flutter แบบเข้าใจและประยุกต์ใช้ได้จริง
+ * สูตรลัด Dart 3 : เรียนรู้ภาษา Dart ก่อนไปเขียนแอปด้วย Flutter
+ * สูตรลัด Dart Frog :  สร้าง REST API ได้ง่ายๆ ด้วยภาษา Dart
+ * สูตรลัด Appwrite : เรียนรู้ Appwrite ฉบับมือโปร เจาะลึกทุกรายละเอียด
+ * สูตรลัด Serverpod : คู่มือการพัฒนาแอปแบบ Fullstack ฉบับสมบูรณ์ด้วยภาษา Dart Flutter และ Serverpod
+ * Prisma Client Dart : เรียนรู้และประยุกต์ใช้ ORM ในการพัฒนาแอปพลิเคชัน
+ * สูตรลัด Jaspr : สร้างเว็บไซต์แบบมือใหม่หัดขับด้วย Jaspr และ Dart
+ * สูตรลัด Bloc :  เริ่มต้นพัฒนาแอป Flutter ด้วยสถาปัตยกรรม BloC
+* เขียนภาษา Go ง่ายนิดเดียว 
+* GORM คู่มือใช้งานฐานข้อมูลใน Go
+ * พัฒนา REST API ด้วยภาษา Go และ Echo
+* สูตรลัด shadcn/ui : คู่มือใช้งาน UI Components สำหรับนักพัฒนา
+* สูตรลัด Next.js: คู่มือสร้างเว็บแอปพลิเคชันสำหรับมือใหม่
+* เอไอเอเจนต์ ฉบับนักพัฒนา: เริ่มจากศูนย์ สู่มือโปร สร้างเอเจนต์อัจฉริยะที่ใช้งานได้จริง
+สนับสนุนช่อง
+* ซื้อหนังสือได้ที่ - https://tinyurl.com/copypastepub
+* ดูไลฟ์ย้อนหลังที่ YouTube - https://tinyurl.com/darthdartlive
+* เรียนออนไลน์ uLearn - https://tinyurl.com/darthdartlearn
+* ดาวน์โหลด UI - https://tinyurl.com/darthdartuikits
+Follow the video playlist  -  https://www.youtube.com/playlist?list=PL1_8_k0Qgcd1bg8tEXZHTp0w0sJskFyo5
+Recorded live video from the Facebook page "Dart แบบ Dart Dart"   https://www.facebook.com/darthdart</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3661</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l1A1cNcb43I</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-02-26T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DevStoriesEU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LiteLLM: The Universal LLM Gateway (v1.82 - 2026 Edition) · 1/24 · The Rosetta Stone of LLMs: The…</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tired of rewriting your API parsing code for every new model? Learn how LiteLLM's Python SDK translates 100+ provider APIs into the exact OpenAI chat completion format. #LiteLLM v1.82 #Python #AI #LLM
+Discover the core identity of LiteLLM: a unified Python interface for over 100 LLMs. Learn how to drop LiteLLM into your existing codebase to call Anthropic, Vertex, or Ollama without changing your OpenAI-compatible parsing logic.
+—
+Free audio courses for developers — no signup, no paywall.
+🎓 Course: LiteLLM: The Universal LLM Gateway (v1.82 - 2026 Edition) · Episode 1 of 24
+🎧 Listen to the full course on Dev Stories EU:
+https://devstories.eu/courses/s3-litellm.html#ep-1
+💚 Support independent dev education on Patreon:
+https://www.patreon.com/c/DevStoriesEU</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>234</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6E76R_cERVY</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-24T12:35:09Z</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Terminal Unlocked</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Drop in llm-router. Remove Lindy. Done.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Drop in llm-router. Remove Lindy. Done..
+Tool: `llm-router` — localhost:11411 — OpenAI-compatible local-first gateway.
+Replaces: Lindy.
+Full stack: https://terminalunlocked.com
+#facelessyoutube #opensource #antisaas</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>53</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wVX2s-xWxE4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-04-28T09:54:16Z</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Terminal Unlocked</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Drop in llm-router. Remove Lindy. Done.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Drop in llm-router. Remove Lindy. Done..
+Tool: `llm-router` — localhost:11411 — OpenAI-compatible local-first gateway.
+Replaces: Lindy.
+Full stack: https://terminalunlocked.com
+#facelessyoutube #opensource #antisaas</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>53</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HRZcjxylhIE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-04-28T18:16:21Z</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Code Rush</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GitHub - ENTERPILOT/GoModel: High-performance AI gateway written in Go - unified OpenAI-compatible A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GoModel - AI Gateway Written in GoA high-performance AI gateway written in Go, providing a unified OpenAI-compatible API for OpenAI, Anthropic, Gemini, xAI, Groq, OpenRouter, Z.ai, Azure OpenAI, Oracle, Ollama, and more.
+For production, use docker run --env-file .env to load API keys from a file instead.
+Step 2: Make your first API callcurl http://localhost:8080/v1/chat/completions \ -H " Content-Type: application/json " \ -d ' { "model": "gpt-5-chat-latest", "messages": [{"role": "user", "content": "Hello!"}]
+Feature columns reflect gateway API support, not every individual model capability exposed by an upstream provider.
+Alternative Setup MethodsRunning from SourcePrerequisites: Go 1.26.2+Create a .env file: cp .env.template .env Add your API keys to .env (at least one required).
+Read more: https://github.com/ENTERPILOT/GOModel/
+#AI #ArtificialIntelligence #MachineLearning #TechAI #AITools #AIBreakthrough</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>61</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t3zQLe5_6xw</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-04-21T17:01:36Z</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>openai compatible llm gateway</t>
         </is>
       </c>
     </row>
@@ -2262,19 +3723,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2326,6 +3787,728 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>app_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>You.com - Enterprise grade AI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SuSea, Inc.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4.75479</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4849</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1600782099</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Locally AI - Local AI Chat</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Element Labs Inc</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4.79061</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1022</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6741426692</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chat with Llama AI - Chatbot</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sozzled LLC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4.43023</v>
+      </c>
+      <c r="F4" t="n">
+        <v>774</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6498941760</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Talky: LLM Playground</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>弓 张</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4.09999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6446136018</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LLM Local Client</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cheuk Yin Lau</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4.44444</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6738433730</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Local LLM: Private Secure Chat</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pocket Bits LLC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>$9.99</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6742779670</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OneLLM : Private &amp; Online LLM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ESOTECH Ltd</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4.55999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6737907910</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pico LLM frontend AI Assistant</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Starling Protocol Inc</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1668205047</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cumbersome: AI LLM API Client</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Folding Sky Co</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4.92307</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6753016821</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LLM Shortcut Toolkit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>kargnas</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4.33333</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6747269378</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ClawOS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Spark Limited Liability Company</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6759203618</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Local LLM Server</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kevin Tang</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3.66667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6757007308</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cisco Jabber</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4.57156</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16742</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>467192391</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Private LLM - Local AI Chat</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Numen Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4.19365</v>
+      </c>
+      <c r="F15" t="n">
+        <v>661</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6448106860</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Liquid Apollo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Liquid AI</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4.51462</v>
+      </c>
+      <c r="F16" t="n">
+        <v>513</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6448019325</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Reins: Chat for Ollama</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ibrahim Cetin</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4.61538</v>
+      </c>
+      <c r="F17" t="n">
+        <v>221</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6739738501</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PocketPal AI</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Asghar Ghorbani</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4.14844</v>
+      </c>
+      <c r="F18" t="n">
+        <v>128</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6502579498</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Google AI Edge Gallery</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4.05511</v>
+      </c>
+      <c r="F19" t="n">
+        <v>127</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6749645337</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AI Chat - Your Smart Assistant</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Neural Techlabs</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4.53333</v>
+      </c>
+      <c r="F20" t="n">
+        <v>90</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6447312365</t>
         </is>
       </c>
     </row>
@@ -2382,10 +4565,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -2434,16 +4617,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>apify</t>
+          <t>analysis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reddit_search</t>
+          <t>cluster_competitors</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -2451,26 +4634,26 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-11 18:45:09</t>
+          <t>2026-05-11 18:52:07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>apify</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tiktok_search</t>
+          <t>search+videos</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2478,26 +4661,26 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-11 18:44:45</t>
+          <t>2026-05-11 18:52:06</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13122</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itunes</t>
+          <t>apify</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>keyword_to_apps_bulk</t>
+          <t>reddit_search</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2505,10 +4688,199 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
+          <t>2026-05-11 18:52:03</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>26767</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>apify</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tiktok_search</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:51:35</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>13183</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ahrefs_hub</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>keywords</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:51:21</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>itunes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lookup_apps</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:51:16</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>itunes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>keyword_to_apps_bulk</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:51:14</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>apify</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>reddit_search</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:45:09</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>23136</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>apify</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>tiktok_search</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:44:45</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>13122</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>itunes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>keyword_to_apps_bulk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>2026-05-11 18:44:31</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G11" t="n">
         <v>1043</v>
       </c>
     </row>
@@ -2910,10 +5282,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.52809</v>
+        <v>4.53333</v>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3090,10 +5462,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.79019</v>
+        <v>4.79061</v>
       </c>
       <c r="F14" t="n">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3306,10 +5678,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.57177</v>
+        <v>4.57156</v>
       </c>
       <c r="F20" t="n">
-        <v>16741</v>
+        <v>16742</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3465,19 +5837,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3529,6 +5901,886 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cisco Jabber</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4.57156</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16742</v>
+      </c>
+      <c r="E2" t="n">
+        <v>837100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1674200</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>467192391</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/cisco-jabber/id467192391?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>You.com - Enterprise grade AI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SuSea, Inc.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4.75479</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4849</v>
+      </c>
+      <c r="E3" t="n">
+        <v>242450</v>
+      </c>
+      <c r="F3" t="n">
+        <v>484900</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1600782099</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/you-com-enterprise-grade-ai/id1600782099?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Locally AI - Local AI Chat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Element Labs Inc</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4.79061</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E4" t="n">
+        <v>51100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>102200</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6741426692</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/locally-ai-local-ai-chat/id6741426692?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chat with Llama AI - Chatbot</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sozzled LLC</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4.43023</v>
+      </c>
+      <c r="D5" t="n">
+        <v>774</v>
+      </c>
+      <c r="E5" t="n">
+        <v>38700</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77400</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6498941760</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/chat-with-llama-ai-chatbot/id6498941760?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Private LLM - Local AI Chat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Numen Technologies Limited</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4.19365</v>
+      </c>
+      <c r="D6" t="n">
+        <v>661</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33050</v>
+      </c>
+      <c r="F6" t="n">
+        <v>66100</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6448106860</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/private-llm-local-ai-chat/id6448106860?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liquid Apollo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Liquid AI</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4.51462</v>
+      </c>
+      <c r="D7" t="n">
+        <v>513</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25650</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51300</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6448019325</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/liquid-apollo/id6448019325?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Reins: Chat for Ollama</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ibrahim Cetin</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4.61538</v>
+      </c>
+      <c r="D8" t="n">
+        <v>221</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11050</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22100</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6739738501</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/reins-chat-for-ollama/id6739738501?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PocketPal AI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Asghar Ghorbani</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4.14844</v>
+      </c>
+      <c r="D9" t="n">
+        <v>128</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6400</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6502579498</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/pocketpal-ai/id6502579498?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Google AI Edge Gallery</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4.05511</v>
+      </c>
+      <c r="D10" t="n">
+        <v>127</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6350</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12700</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6749645337</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/google-ai-edge-gallery/id6749645337?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Chat - Your Smart Assistant</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Neural Techlabs</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4.53333</v>
+      </c>
+      <c r="D11" t="n">
+        <v>90</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6447312365</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/ai-chat-your-smart-assistant/id6447312365?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OneLLM : Private &amp; Online LLM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ESOTECH Ltd</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4.55999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6737907910</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/onellm-private-online-llm/id6737907910?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pico LLM frontend AI Assistant</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Starling Protocol Inc</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1668205047</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/pico-llm-frontend-ai-assistant/id1668205047?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cumbersome: AI LLM API Client</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Folding Sky Co</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4.92307</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>650</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6753016821</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/cumbersome-ai-llm-api-client/id6753016821?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Talky: LLM Playground</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>弓 张</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.09999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>500</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6446136018</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/talky-llm-playground/id6446136018?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LLM Local Client</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cheuk Yin Lau</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4.44444</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>450</v>
+      </c>
+      <c r="F16" t="n">
+        <v>900</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6738433730</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/llm-local-client/id6738433730?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LLM Shortcut Toolkit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>kargnas</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4.33333</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>300</v>
+      </c>
+      <c r="F17" t="n">
+        <v>600</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6747269378</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/llm-shortcut-toolkit/id6747269378?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ClawOS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Spark Limited Liability Company</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>300</v>
+      </c>
+      <c r="F18" t="n">
+        <v>600</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6759203618</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/clawos/id6759203618?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Local LLM Server</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kevin Tang</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3.66667</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>150</v>
+      </c>
+      <c r="F19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6757007308</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/local-llm-server/id6757007308?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Local LLM: Private Secure Chat</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pocket Bits LLC</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>$9.99</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6742779670</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/local-llm-private-secure-chat/id6742779670?uo=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FishLLM - Local LLM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>志亮 黎</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6504334099</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/fishllm-local-llm/id6504334099?uo=4</t>
         </is>
       </c>
     </row>
